--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="41">
   <si>
     <t>Email</t>
   </si>
@@ -146,6 +146,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -510,11 +511,11 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="10.6640625"/>
+    <col min="2" max="2" customWidth="true" width="18.0"/>
+    <col min="3" max="3" customWidth="true" width="20.6640625"/>
+    <col min="4" max="4" customWidth="true" width="11.77734375"/>
+    <col min="5" max="5" customWidth="true" width="13.33203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.8">
@@ -607,8 +608,8 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="19.33203125"/>
+    <col min="2" max="2" customWidth="true" width="14.6640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -658,8 +659,8 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="14.6640625"/>
+    <col min="2" max="2" customWidth="true" width="14.88671875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -704,15 +705,15 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="17.21875" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="17.21875"/>
+    <col min="2" max="2" customWidth="true" width="12.6640625"/>
+    <col min="3" max="3" customWidth="true" width="13.21875"/>
+    <col min="4" max="4" customWidth="true" width="13.6640625"/>
+    <col min="5" max="5" customWidth="true" width="12.109375"/>
+    <col min="6" max="6" customWidth="true" width="14.109375"/>
+    <col min="7" max="7" customWidth="true" width="14.77734375"/>
+    <col min="9" max="9" customWidth="true" width="12.44140625"/>
+    <col min="10" max="10" customWidth="true" width="14.5546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -748,98 +749,98 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="0">
         <v>123456</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="0">
         <v>11111111</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="0">
         <v>11</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>2026</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="0">
         <v>280004</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="0">
         <v>22222222</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="0">
         <v>12</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="0">
         <v>2025</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" t="s" s="0">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="0">
         <v>110045</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="0">
         <v>33333333</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="0">
         <v>13</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="0">
         <v>2024</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" t="s" s="0">
         <v>28</v>
       </c>
     </row>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="41">
   <si>
     <t>Email</t>
   </si>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="41">
   <si>
     <t>Email</t>
   </si>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="41">
   <si>
     <t>Email</t>
   </si>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="41">
   <si>
     <t>Email</t>
   </si>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="41">
   <si>
     <t>Email</t>
   </si>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="41">
   <si>
     <t>Email</t>
   </si>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="41">
   <si>
     <t>Email</t>
   </si>
